--- a/data/trans_dic/P41E_2023_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,62</t>
+          <t>3,93; 8,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,6</t>
+          <t>4,2; 9,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,91</t>
+          <t>4,56; 7,85</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 14,91</t>
+          <t>7,26; 14,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,04</t>
+          <t>4,19; 10,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,73</t>
+          <t>6,46; 11,19</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 15,08</t>
+          <t>1,96; 15,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 25,36</t>
+          <t>12,53; 25,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 16,06</t>
+          <t>2,89; 16,08</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 15,84</t>
+          <t>10,25; 15,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,61</t>
+          <t>1,76; 8,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,25</t>
+          <t>4,36; 11,35</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 19,44</t>
+          <t>11,25; 19,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,15; 21,09</t>
+          <t>15,04; 21,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 19,32</t>
+          <t>14,36; 19,09</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 31,23</t>
+          <t>3,92; 31,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,79; 25,21</t>
+          <t>16,74; 25,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,06; 23,87</t>
+          <t>15,95; 23,88</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,0</t>
+          <t>5,98; 12,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,17</t>
+          <t>6,51; 13,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,27</t>
+          <t>7,73; 12,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10995; 24204</t>
+          <t>11025; 24485</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9270; 20987</t>
+          <t>9186; 20324</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22920; 39517</t>
+          <t>22763; 39171</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17832; 34999</t>
+          <t>17046; 33503</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7821; 19235</t>
+          <t>8024; 19521</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28605; 49976</t>
+          <t>27538; 47694</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10059; 71394</t>
+          <t>9301; 71830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9683; 20404</t>
+          <t>10086; 20345</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17014; 88924</t>
+          <t>16027; 89060</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48689; 74912</t>
+          <t>48490; 74225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10559; 48345</t>
+          <t>9880; 49239</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48097; 116393</t>
+          <t>45142; 117359</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25053; 43842</t>
+          <t>25369; 44004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51283; 71383</t>
+          <t>50898; 71265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81812; 108974</t>
+          <t>81011; 107689</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1226; 14344</t>
+          <t>1800; 14431</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43058; 64640</t>
+          <t>42910; 64157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48560; 72180</t>
+          <t>48237; 72191</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>110502; 208013</t>
+          <t>103718; 211325</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122857; 216800</t>
+          <t>107258; 216208</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273208; 414807</t>
+          <t>261276; 411557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,72</t>
+          <t>3,82; 8,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,3</t>
+          <t>4,24; 9,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,85</t>
+          <t>4,41; 7,86</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 14,28</t>
+          <t>7,32; 14,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,19</t>
+          <t>4,15; 9,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,19</t>
+          <t>6,8; 11,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 15,18</t>
+          <t>10,0; 17,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 25,28</t>
+          <t>11,94; 24,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,08</t>
+          <t>11,35; 18,26</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,69</t>
+          <t>10,19; 15,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,77</t>
+          <t>5,47; 10,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,35</t>
+          <t>8,72; 12,15</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 19,51</t>
+          <t>11,25; 19,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,04; 21,05</t>
+          <t>14,49; 20,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 19,09</t>
+          <t>14,04; 18,88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 31,41</t>
+          <t>2,97; 28,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,74; 25,02</t>
+          <t>17,09; 25,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,95; 23,88</t>
+          <t>16,29; 24,86</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,19</t>
+          <t>10,03; 12,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 13,13</t>
+          <t>11,31; 13,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,18</t>
+          <t>10,96; 12,93</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>33188</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11025; 24485</t>
+          <t>11768; 26170</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9186; 20324</t>
+          <t>10146; 22589</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22763; 39171</t>
+          <t>24117; 43036</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>40191</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17046; 33503</t>
+          <t>18429; 36704</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8024; 19521</t>
+          <t>8734; 20885</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27538; 47694</t>
+          <t>31418; 52240</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>49533</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9301; 71830</t>
+          <t>25100; 44507</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10086; 20345</t>
+          <t>10718; 22341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16027; 89060</t>
+          <t>38656; 62213</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>64955</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>94695</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48490; 74225</t>
+          <t>53030; 78792</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9880; 49239</t>
+          <t>21661; 40056</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45142; 117359</t>
+          <t>79844; 111263</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33774</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>66193</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94813</t>
+          <t>103528</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25369; 44004</t>
+          <t>28633; 48860</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50898; 71265</t>
+          <t>54519; 76977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81011; 107689</t>
+          <t>88550; 119089</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>53348</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59163</t>
+          <t>64675</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1800; 14431</t>
+          <t>1346; 12894</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42910; 64157</t>
+          <t>47781; 72017</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48237; 72191</t>
+          <t>52935; 80758</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>173033</t>
+          <t>185172</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>356140</t>
+          <t>385811</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>103718; 211325</t>
+          <t>163574; 210903</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107258; 216208</t>
+          <t>179884; 221202</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>261276; 411557</t>
+          <t>353011; 416635</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
